--- a/public/policy_templates/drgadget_claim_import_template.xlsx
+++ b/public/policy_templates/drgadget_claim_import_template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FS-User\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\friendsure\admin-portal\public\policy_templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F26D8DCD-5A91-4DC8-A274-ACBDE7CC3B5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAC2868C-8ED2-4F61-878F-911B92DFA476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1480" yWindow="1480" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,14 +31,14 @@
     <t>Submitted</t>
   </si>
   <si>
-    <t>DRGCSP-20250717-0001</t>
+    <t>DRGCSP-20250716-0045</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -55,9 +55,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Inter"/>
+      <sz val="12"/>
+      <color rgb="FFD1977F"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -406,13 +407,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -420,7 +421,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
